--- a/estimator.xlsx
+++ b/estimator.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jason\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Server\panel-scheduler\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>

--- a/estimator.xlsx
+++ b/estimator.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="82">
   <si>
     <t>Customer:</t>
   </si>
@@ -267,9 +267,6 @@
   </si>
   <si>
     <t>Notes:</t>
-  </si>
-  <si>
-    <t>8109-600</t>
   </si>
   <si>
     <t>60Hp VFD</t>
@@ -6343,14 +6340,14 @@
       <c r="A276" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B276" s="1" t="s">
+      <c r="B276" s="1">
+        <v>8109</v>
+      </c>
+      <c r="C276" s="1">
+        <v>1</v>
+      </c>
+      <c r="D276" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="C276" s="1">
-        <v>1</v>
-      </c>
-      <c r="D276" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="F276" s="1">
         <v>12</v>

--- a/estimator.xlsx
+++ b/estimator.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="83">
   <si>
     <t>Customer:</t>
   </si>
@@ -267,6 +267,9 @@
   </si>
   <si>
     <t>Notes:</t>
+  </si>
+  <si>
+    <t>8109-600</t>
   </si>
   <si>
     <t>60Hp VFD</t>
@@ -6340,14 +6343,14 @@
       <c r="A276" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B276" s="1">
-        <v>8109</v>
+      <c r="B276" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="C276" s="1">
         <v>1</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F276" s="1">
         <v>12</v>
